--- a/mlef_pipeline/results/OS_24/SQUAMOUS/RWD_DP_FMRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_24/SQUAMOUS/RWD_DP_FMRAD/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.41 ± 0.32</t>
+          <t>0.55 ± 0.27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.33 ± 0.19</t>
+          <t>0.20 ± 0.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.15 ± 0.36</t>
+          <t>0.46 ± 0.50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.65 ± 0.48</t>
+          <t>0.37 ± 0.48</t>
         </is>
       </c>
       <c r="F2" t="n">

--- a/mlef_pipeline/results/OS_24/SQUAMOUS/RWD_DP_FMRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_24/SQUAMOUS/RWD_DP_FMRAD/rwd-only/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
